--- a/data/trans_orig/IP13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>87321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94914</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190124</t>
+          <t>189997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198194</t>
+          <t>198209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79503</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86021</t>
+          <t>86031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76892</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>84065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159625</t>
+          <t>159436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168577</t>
+          <t>168548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65974</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91972</t>
+          <t>91894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98020</t>
+          <t>97995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153957</t>
+          <t>153819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162706</t>
+          <t>162569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184138</t>
+          <t>184254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194741</t>
+          <t>194325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184297</t>
+          <t>184646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195578</t>
+          <t>195260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372615</t>
+          <t>373050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387630</t>
+          <t>386956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95981</t>
+          <t>95890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102757</t>
+          <t>102754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>116489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124578</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216113</t>
+          <t>215675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226161</t>
+          <t>225662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67757</t>
+          <t>67617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73641</t>
+          <t>73587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>63187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69890</t>
+          <t>69895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133550</t>
+          <t>133591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142192</t>
+          <t>142730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37397</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>27696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76806</t>
+          <t>76230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601459</t>
+          <t>602393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>618521</t>
+          <t>618469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638494</t>
+          <t>638153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>657185</t>
+          <t>656907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246653</t>
+          <t>1247229</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1271852</t>
+          <t>1271447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81237</t>
+          <t>81440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88500</t>
+          <t>88478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81498</t>
+          <t>82072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88551</t>
+          <t>88483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166130</t>
+          <t>166426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175707</t>
+          <t>175678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>80445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>89443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95425</t>
+          <t>95415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172743</t>
+          <t>171694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183116</t>
+          <t>183369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75516</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83608</t>
+          <t>83798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>78873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157186</t>
+          <t>156927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167685</t>
+          <t>167604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>39235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190564</t>
+          <t>191017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201008</t>
+          <t>201067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199912</t>
+          <t>200209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214446</t>
+          <t>213627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395042</t>
+          <t>393994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412170</t>
+          <t>412019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132300</t>
+          <t>131709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142638</t>
+          <t>142566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127684</t>
+          <t>126807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136356</t>
+          <t>136191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263589</t>
+          <t>263718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277170</t>
+          <t>276673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63381</t>
+          <t>63419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116090</t>
+          <t>115986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124520</t>
+          <t>124570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47930</t>
+          <t>48696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32793</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>53612</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94450</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629405</t>
+          <t>628639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648703</t>
+          <t>648984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660166</t>
+          <t>659947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680766</t>
+          <t>680406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1296444</t>
+          <t>1292612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1324929</t>
+          <t>1323054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81051</t>
+          <t>81237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170129</t>
+          <t>170601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178944</t>
+          <t>179128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100777</t>
+          <t>100650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105144</t>
+          <t>105147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103277</t>
+          <t>102662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110310</t>
+          <t>110328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206595</t>
+          <t>206387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>214819</t>
+          <t>214728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>60036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>65212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>73019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122811</t>
+          <t>122719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>132572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23779</t>
+          <t>24766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199798</t>
+          <t>198811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211726</t>
+          <t>211804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205640</t>
+          <t>205110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399331</t>
+          <t>398253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414597</t>
+          <t>414584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126870</t>
+          <t>127010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133858</t>
+          <t>134415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132012</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140118</t>
+          <t>140167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260966</t>
+          <t>261857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272529</t>
+          <t>272615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54818</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61180</t>
+          <t>61986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67211</t>
+          <t>67220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119669</t>
+          <t>119384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126981</t>
+          <t>127258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47140</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>40172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79063</t>
+          <t>79936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>624362</t>
+          <t>625495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644118</t>
+          <t>644070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>669695</t>
+          <t>669565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688087</t>
+          <t>688101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1302176</t>
+          <t>1301303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1329010</t>
+          <t>1327886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93172</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>101210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125432</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134255</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222118</t>
+          <t>222274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234503</t>
+          <t>234109</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>84628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92532</t>
+          <t>92616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90482</t>
+          <t>90529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168994</t>
+          <t>169391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181393</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50816</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55635</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62553</t>
+          <t>62683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104494</t>
+          <t>104289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112453</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202395</t>
+          <t>202444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213329</t>
+          <t>213574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>193975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208535</t>
+          <t>208633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401347</t>
+          <t>401811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419328</t>
+          <t>419707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28896</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>103150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113497</t>
+          <t>113182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145950</t>
+          <t>146601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156892</t>
+          <t>157023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>253149</t>
+          <t>252786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268493</t>
+          <t>267812</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>61064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>71121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128088</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137490</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48291</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>58986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68448</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99738</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609046</t>
+          <t>609653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>629110</t>
+          <t>629172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687738</t>
+          <t>689516</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712691</t>
+          <t>713063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1306101</t>
+          <t>1305670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1337391</t>
+          <t>1337325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
